--- a/leagueStats/leagueStats_ITA_2126.xlsx
+++ b/leagueStats/leagueStats_ITA_2126.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,6 +1010,414 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.207477491348975</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.802410388365395</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.440000057220459</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.128107739612463</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.109575491398585</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.309999942779541</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.210000038146973</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.713690203614533</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9836800275370532</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.659999966621399</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.190000057220459</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.845152139663701</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.259612673893567</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.879999995231628</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9700000286102295</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.580977836623793</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.251603018492458</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.679999947547913</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3600000143051147</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SSC Napoli</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.385439096949993</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.049160877242685</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.659999966621399</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.360000014305115</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.484042005613444</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.669219701550896</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5400000214576721</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.619976196438079</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.423799522221094</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.230000019073486</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6200000047683716</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leagueStats/leagueStats_ITA_2126.xlsx
+++ b/leagueStats/leagueStats_ITA_2126.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.802410388365395</v>
       </c>
       <c r="H12" t="n">
-        <v>2.440000057220459</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="M12" t="n">
         <v>0.19</v>
       </c>
       <c r="N12" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>

--- a/leagueStats/leagueStats_ITA_2126.xlsx
+++ b/leagueStats/leagueStats_ITA_2126.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,108 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.798627180978652</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.335564428940414</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8399999737739563</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.410000085830688</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.153543850407005</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.053039767779403</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2800000011920929</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9900000095367432</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leagueStats/leagueStats_ITA_2126.xlsx
+++ b/leagueStats/leagueStats_ITA_2126.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,6 +1520,516 @@
         <v>1</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7844457384198922</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.783048480749128</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.129999995231628</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.600000023841858</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.753435920923952</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5776587948203029</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.460000038146973</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7200000286102295</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SSC Napoli</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.855111261829727</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.450653785839666</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.070000171661377</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.150000095367432</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.965938048437235</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.701700279489159</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.490000009536743</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7799999713897705</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.89855673536658</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.168732321821147</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.330000042915344</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.940000057220459</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7306813672184941</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.719373759813597</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.029999971389771</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.460000038146973</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.894212461076664</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.623977459967147</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.460000038146973</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.661848642863345</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1060016294941309</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.350000023841858</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1299999952316284</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.605210743844518</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5039338287897324</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.409999966621399</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7300000190734863</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.857091644778856</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.83302219212055</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8799999952316284</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.809999942779541</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/leagueStats/leagueStats_ITA_2126.xlsx
+++ b/leagueStats/leagueStats_ITA_2126.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,83 +413,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>homeTeam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>awayTeam</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>homeScore</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>awayScore</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>homeXg</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>awayXg</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>homeXgPred</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>awayXgPred</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>homePred</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>awayPred</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>homeDiff</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>awayDiff</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>totalDiff</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>goalDiff</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,7 +540,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -603,7 +591,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -705,7 +693,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -756,7 +744,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -807,7 +795,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -858,7 +846,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -909,7 +897,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -960,7 +948,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1011,7 +999,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1062,7 +1050,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1113,7 +1101,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1164,7 +1152,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1215,7 +1203,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1266,7 +1254,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1317,7 +1305,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1368,7 +1356,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1419,7 +1407,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1470,7 +1458,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1521,7 +1509,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1572,7 +1560,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1623,7 +1611,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1674,7 +1662,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1725,7 +1713,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1776,7 +1764,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1827,7 +1815,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1878,7 +1866,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1929,7 +1917,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1980,7 +1968,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2028,6 +2016,516 @@
       </c>
       <c r="O31" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.485689665190882</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.686903383582822</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7099999785423279</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.876545733810958</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.930661867372692</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.070000052452087</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.899999976158142</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.014237904921168</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.251003513112665</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.289999961853027</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.559999942779541</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.74203507509082</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.321564632506667</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.669999957084656</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.072117023169989</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.524599858559686</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.110000014305115</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.450000047683716</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SSC Napoli</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.191013220697641</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.291887044906614</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2899999916553497</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.024288760963823</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.097553418017919</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9100000262260437</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.330000042915344</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.021417265757925</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.146150567568844</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.119999885559082</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.210000038146973</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.8552376534789869</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.954588424414393</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6800000071525574</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.960000038146973</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.203751466236998</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.922459743916991</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.660000085830688</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O41" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
